--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-person.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-person.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-person|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-person|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -388,7 +388,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-person|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-person|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Person.meta.security</t>
@@ -655,7 +655,7 @@
     <t>as-ext-person-birth-place</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -675,7 +675,7 @@
     <t>as-ext-person-deceased-date-time</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -691,7 +691,7 @@
     <t>as-ext-person-statut-etat-civil</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-statut-etat-civil|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-statut-etat-civil|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1369,7 +1369,7 @@
     <t>Person.link:as-practitioner-exercice-professionnel.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-person.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-person.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
